--- a/Cafe_Dishes_Template.xlsx
+++ b/Cafe_Dishes_Template.xlsx
@@ -1,41 +1,494 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView xWindow="130" yWindow="610" windowWidth="18880" windowHeight="6490"/>
+  </bookViews>
   <sheets>
-    <sheet name="Cafe Menu Template" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="156">
+  <si>
+    <t>Dish Name</t>
+  </si>
+  <si>
+    <t>Portions</t>
+  </si>
+  <si>
+    <t>Wastage %</t>
+  </si>
+  <si>
+    <t>Ingredient Name</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Grams/Ml</t>
+  </si>
+  <si>
+    <t>UOM</t>
+  </si>
+  <si>
+    <t>Is Base</t>
+  </si>
+  <si>
+    <t>ALFREDO MACARONI</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for ALFREDO MACARONI</t>
+  </si>
+  <si>
+    <t>GM</t>
+  </si>
+  <si>
+    <t>GRM</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for ALFREDO MACARONI</t>
+  </si>
+  <si>
+    <t>ML</t>
+  </si>
+  <si>
+    <t>ARRABBIATA SPAGHETTI</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for ARRABBIATA SPAGHETTI</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for ARRABBIATA SPAGHETTI</t>
+  </si>
+  <si>
+    <t>Bang bang cauliflower</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for Bang bang cauliflower</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for Bang bang cauliflower</t>
+  </si>
+  <si>
+    <t>CEASAR SALAD</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for CEASAR SALAD</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for CEASAR SALAD</t>
+  </si>
+  <si>
+    <t>Carrot Pineapple and Lemo</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for Carrot Pineapple and Lemo</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for Carrot Pineapple and Lemo</t>
+  </si>
+  <si>
+    <t>Crisp Jackfruit Bites</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for Crisp Jackfruit Bites</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for Crisp Jackfruit Bites</t>
+  </si>
+  <si>
+    <t>Dal Khakra chaat</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for Dal Khakra chaat</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for Dal Khakra chaat</t>
+  </si>
+  <si>
+    <t>Desi Veg Burger</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for Desi Veg Burger</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for Desi Veg Burger</t>
+  </si>
+  <si>
+    <t>FARM FRESH PIZZA</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for FARM FRESH PIZZA</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for FARM FRESH PIZZA</t>
+  </si>
+  <si>
+    <t>GREEK BOWL</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for GREEK BOWL</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for GREEK BOWL</t>
+  </si>
+  <si>
+    <t>GREEK SALAD</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for GREEK SALAD</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for GREEK SALAD</t>
+  </si>
+  <si>
+    <t>HIGH PROTEIN PASTA</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for HIGH PROTEIN PASTA</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for HIGH PROTEIN PASTA</t>
+  </si>
+  <si>
+    <t>JACKFRUIT KHEEMA KULCHA</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for JACKFRUIT KHEEMA KULCHA</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for JACKFRUIT KHEEMA KULCHA</t>
+  </si>
+  <si>
+    <t>LEEK AND ASPARAGUS SOUP</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for LEEK AND ASPARAGUS SOUP</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for LEEK AND ASPARAGUS SOUP</t>
+  </si>
+  <si>
+    <t>MAKHAN DAHI VADA</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for MAKHAN DAHI VADA</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for MAKHAN DAHI VADA</t>
+  </si>
+  <si>
+    <t>MEXICAN BOWL</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for MEXICAN BOWL</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for MEXICAN BOWL</t>
+  </si>
+  <si>
+    <t>MEXICAN SALAD</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for MEXICAN SALAD</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for MEXICAN SALAD</t>
+  </si>
+  <si>
+    <t>MINT LEMONADE</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for MINT LEMONADE</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for MINT LEMONADE</t>
+  </si>
+  <si>
+    <t>Mediterranean Sourdough Sandwic</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for Mediterranean Sourdough Sandwic</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for Mediterranean Sourdough Sandwic</t>
+  </si>
+  <si>
+    <t>Namma Chip &amp; dip platter</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for Namma Chip &amp; dip platter</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for Namma Chip &amp; dip platter</t>
+  </si>
+  <si>
+    <t>PANEER BHURJI KULCHA</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for PANEER BHURJI KULCHA</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for PANEER BHURJI KULCHA</t>
+  </si>
+  <si>
+    <t>PANEER SATAY</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for PANEER SATAY</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for PANEER SATAY</t>
+  </si>
+  <si>
+    <t>PANEER SRIRACHA PIZZA</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for PANEER SRIRACHA PIZZA</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for PANEER SRIRACHA PIZZA</t>
+  </si>
+  <si>
+    <t>PESTO PASTA</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for PESTO PASTA</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for PESTO PASTA</t>
+  </si>
+  <si>
+    <t>PHAD THAI</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for PHAD THAI</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for PHAD THAI</t>
+  </si>
+  <si>
+    <t>PIZZA BASE 1</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for PIZZA BASE 1</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for PIZZA BASE 1</t>
+  </si>
+  <si>
+    <t>PUMPKIN SOUP</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for PUMPKIN SOUP</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for PUMPKIN SOUP</t>
+  </si>
+  <si>
+    <t>PURE SURE JUICE</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for PURE SURE JUICE</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for PURE SURE JUICE</t>
+  </si>
+  <si>
+    <t>PURE SURE SALAD</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for PURE SURE SALAD</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for PURE SURE SALAD</t>
+  </si>
+  <si>
+    <t>Palak Tofu Cheela</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for Palak Tofu Cheela</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for Palak Tofu Cheela</t>
+  </si>
+  <si>
+    <t>Pancharatna Dal with Rice</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for Pancharatna Dal with Rice</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for Pancharatna Dal with Rice</t>
+  </si>
+  <si>
+    <t>Paneer Butter Masala</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for Paneer Butter Masala</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for Paneer Butter Masala</t>
+  </si>
+  <si>
+    <t>QUINOA SALAD</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for QUINOA SALAD</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for QUINOA SALAD</t>
+  </si>
+  <si>
+    <t>Quinoa bites</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for Quinoa bites</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for Quinoa bites</t>
+  </si>
+  <si>
+    <t>SPINACH AND CORN</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for SPINACH AND CORN</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for SPINACH AND CORN</t>
+  </si>
+  <si>
+    <t>SUPER FOOD SALAD</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for SUPER FOOD SALAD</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for SUPER FOOD SALAD</t>
+  </si>
+  <si>
+    <t>SWEET POTATO FRIES - PICK UP</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for SWEET POTATO FRIES - PICK UP</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for SWEET POTATO FRIES - PICK UP</t>
+  </si>
+  <si>
+    <t>Spaghetti Aglio e Olio</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for Spaghetti Aglio e Olio</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for Spaghetti Aglio e Olio</t>
+  </si>
+  <si>
+    <t>THAI CURRY</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for THAI CURRY</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for THAI CURRY</t>
+  </si>
+  <si>
+    <t>TOFU BROCCOLI PEANUT SALAD</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for TOFU BROCCOLI PEANUT SALAD</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for TOFU BROCCOLI PEANUT SALAD</t>
+  </si>
+  <si>
+    <t>TOM YUM NOODLE SOUP</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for TOM YUM NOODLE SOUP</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for TOM YUM NOODLE SOUP</t>
+  </si>
+  <si>
+    <t>TOMATO SOUP</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for TOMATO SOUP</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for TOMATO SOUP</t>
+  </si>
+  <si>
+    <t>Veg Clear Soup</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for Veg Clear Soup</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for Veg Clear Soup</t>
+  </si>
+  <si>
+    <t>WHITE SAUCE PASTA</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for WHITE SAUCE PASTA</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for WHITE SAUCE PASTA</t>
+  </si>
+  <si>
+    <t>crispy veg Burger</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for crispy veg Burger</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for crispy veg Burger</t>
+  </si>
+  <si>
+    <t>millet Bisibele Bath</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for millet Bisibele Bath</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for millet Bisibele Bath</t>
+  </si>
+  <si>
+    <t>mixed millet biryani</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for mixed millet biryani</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for mixed millet biryani</t>
+  </si>
+  <si>
+    <t>paneer ghee roast open burger</t>
+  </si>
+  <si>
+    <t>Organic Base Ingredient for paneer ghee roast open burger</t>
+  </si>
+  <si>
+    <t>Organic Seasoning for paneer ghee roast open burger</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -72,6 +525,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,108 +854,2833 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I97"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.4140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>type</v>
-      </c>
-      <c r="B1" t="str">
-        <v>name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>category</v>
-      </c>
-      <c r="D1" t="str">
-        <v>price</v>
-      </c>
-      <c r="E1" t="str">
-        <v>desc</v>
-      </c>
-      <c r="F1" t="str">
-        <v>badges</v>
-      </c>
-      <c r="G1" t="str">
-        <v>cal</v>
-      </c>
-      <c r="H1" t="str">
-        <v>protein</v>
-      </c>
-      <c r="I1" t="str">
-        <v>carbs</v>
-      </c>
-      <c r="J1" t="str">
-        <v>fat</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>cafe</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Ragi Masala Dosa</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Breakfast</v>
-      </c>
-      <c r="D2">
-        <v>160</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Stone-ground ragi batter with potato masala</v>
-      </c>
-      <c r="F2" t="str">
-        <v>100% Organic, Gluten-Free</v>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
       </c>
       <c r="G2">
-        <v>280</v>
-      </c>
-      <c r="H2">
-        <v>8</v>
-      </c>
-      <c r="I2">
+        <v>100</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3">
+        <v>20</v>
+      </c>
+      <c r="G3">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5">
+        <v>20</v>
+      </c>
+      <c r="G5">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>20</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8">
+        <v>100</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9">
+        <v>20</v>
+      </c>
+      <c r="G9">
+        <v>20</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10">
+        <v>100</v>
+      </c>
+      <c r="G10">
+        <v>100</v>
+      </c>
+      <c r="H10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11">
+        <v>20</v>
+      </c>
+      <c r="G11">
+        <v>20</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12">
+        <v>100</v>
+      </c>
+      <c r="G12">
+        <v>100</v>
+      </c>
+      <c r="H12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13">
+        <v>20</v>
+      </c>
+      <c r="G13">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14">
+        <v>100</v>
+      </c>
+      <c r="G14">
+        <v>100</v>
+      </c>
+      <c r="H14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15">
+        <v>20</v>
+      </c>
+      <c r="G15">
+        <v>20</v>
+      </c>
+      <c r="H15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16">
+        <v>100</v>
+      </c>
+      <c r="G16">
+        <v>100</v>
+      </c>
+      <c r="H16" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17">
+        <v>20</v>
+      </c>
+      <c r="G17">
+        <v>20</v>
+      </c>
+      <c r="H17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18">
+        <v>100</v>
+      </c>
+      <c r="G18">
+        <v>100</v>
+      </c>
+      <c r="H18" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19">
+        <v>20</v>
+      </c>
+      <c r="G19">
+        <v>20</v>
+      </c>
+      <c r="H19" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20">
+        <v>100</v>
+      </c>
+      <c r="G20">
+        <v>100</v>
+      </c>
+      <c r="H20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21">
+        <v>20</v>
+      </c>
+      <c r="G21">
+        <v>20</v>
+      </c>
+      <c r="H21" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>42</v>
       </c>
-      <c r="J2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>cafe</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Turmeric Ginger Latte</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Beverages</v>
-      </c>
-      <c r="D3">
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22">
+        <v>100</v>
+      </c>
+      <c r="G22">
+        <v>100</v>
+      </c>
+      <c r="H22" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23">
+        <v>20</v>
+      </c>
+      <c r="G23">
+        <v>20</v>
+      </c>
+      <c r="H23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24">
+        <v>100</v>
+      </c>
+      <c r="G24">
+        <v>100</v>
+      </c>
+      <c r="H24" t="s">
+        <v>12</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+      <c r="D25" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25">
+        <v>20</v>
+      </c>
+      <c r="G25">
+        <v>20</v>
+      </c>
+      <c r="H25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26">
+        <v>100</v>
+      </c>
+      <c r="G26">
+        <v>100</v>
+      </c>
+      <c r="H26" t="s">
+        <v>12</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+      <c r="D27" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27">
+        <v>20</v>
+      </c>
+      <c r="G27">
+        <v>20</v>
+      </c>
+      <c r="H27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28">
+        <v>100</v>
+      </c>
+      <c r="G28">
+        <v>100</v>
+      </c>
+      <c r="H28" t="s">
+        <v>12</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29">
+        <v>20</v>
+      </c>
+      <c r="G29">
+        <v>20</v>
+      </c>
+      <c r="H29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>3</v>
+      </c>
+      <c r="D30" t="s">
+        <v>55</v>
+      </c>
+      <c r="E30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30">
+        <v>100</v>
+      </c>
+      <c r="G30">
+        <v>100</v>
+      </c>
+      <c r="H30" t="s">
+        <v>12</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31">
+        <v>20</v>
+      </c>
+      <c r="G31">
+        <v>20</v>
+      </c>
+      <c r="H31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32" t="s">
+        <v>58</v>
+      </c>
+      <c r="E32" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32">
+        <v>100</v>
+      </c>
+      <c r="G32">
+        <v>100</v>
+      </c>
+      <c r="H32" t="s">
+        <v>12</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+      <c r="D33" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33">
+        <v>20</v>
+      </c>
+      <c r="G33">
+        <v>20</v>
+      </c>
+      <c r="H33" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34" t="s">
+        <v>61</v>
+      </c>
+      <c r="E34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34">
+        <v>100</v>
+      </c>
+      <c r="G34">
+        <v>100</v>
+      </c>
+      <c r="H34" t="s">
+        <v>12</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35">
+        <v>3</v>
+      </c>
+      <c r="D35" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35">
+        <v>20</v>
+      </c>
+      <c r="G35">
+        <v>20</v>
+      </c>
+      <c r="H35" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36">
+        <v>3</v>
+      </c>
+      <c r="D36" t="s">
+        <v>64</v>
+      </c>
+      <c r="E36" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36">
+        <v>100</v>
+      </c>
+      <c r="G36">
+        <v>100</v>
+      </c>
+      <c r="H36" t="s">
+        <v>12</v>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
+      <c r="D37" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37">
+        <v>20</v>
+      </c>
+      <c r="G37">
+        <v>20</v>
+      </c>
+      <c r="H37" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
+      </c>
+      <c r="D38" t="s">
+        <v>67</v>
+      </c>
+      <c r="E38" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38">
+        <v>100</v>
+      </c>
+      <c r="G38">
+        <v>100</v>
+      </c>
+      <c r="H38" t="s">
+        <v>12</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39" t="s">
+        <v>68</v>
+      </c>
+      <c r="E39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39">
+        <v>20</v>
+      </c>
+      <c r="G39">
+        <v>20</v>
+      </c>
+      <c r="H39" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
+      <c r="D40" t="s">
+        <v>70</v>
+      </c>
+      <c r="E40" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40">
+        <v>100</v>
+      </c>
+      <c r="G40">
+        <v>100</v>
+      </c>
+      <c r="H40" t="s">
+        <v>12</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41">
+        <v>3</v>
+      </c>
+      <c r="D41" t="s">
+        <v>71</v>
+      </c>
+      <c r="E41" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41">
+        <v>20</v>
+      </c>
+      <c r="G41">
+        <v>20</v>
+      </c>
+      <c r="H41" t="s">
+        <v>14</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>72</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>3</v>
+      </c>
+      <c r="D42" t="s">
+        <v>73</v>
+      </c>
+      <c r="E42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42">
+        <v>100</v>
+      </c>
+      <c r="G42">
+        <v>100</v>
+      </c>
+      <c r="H42" t="s">
+        <v>12</v>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>72</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+      <c r="D43" t="s">
+        <v>74</v>
+      </c>
+      <c r="E43" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43">
+        <v>20</v>
+      </c>
+      <c r="G43">
+        <v>20</v>
+      </c>
+      <c r="H43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
+      <c r="D44" t="s">
+        <v>76</v>
+      </c>
+      <c r="E44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44">
+        <v>100</v>
+      </c>
+      <c r="G44">
+        <v>100</v>
+      </c>
+      <c r="H44" t="s">
+        <v>12</v>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>75</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+      <c r="D45" t="s">
+        <v>77</v>
+      </c>
+      <c r="E45" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45">
+        <v>20</v>
+      </c>
+      <c r="G45">
+        <v>20</v>
+      </c>
+      <c r="H45" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>78</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>3</v>
+      </c>
+      <c r="D46" t="s">
+        <v>79</v>
+      </c>
+      <c r="E46" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46">
+        <v>100</v>
+      </c>
+      <c r="G46">
+        <v>100</v>
+      </c>
+      <c r="H46" t="s">
+        <v>12</v>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+      <c r="D47" t="s">
+        <v>80</v>
+      </c>
+      <c r="E47" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47">
+        <v>20</v>
+      </c>
+      <c r="G47">
+        <v>20</v>
+      </c>
+      <c r="H47" t="s">
+        <v>14</v>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>81</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48">
+        <v>3</v>
+      </c>
+      <c r="D48" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48">
+        <v>100</v>
+      </c>
+      <c r="G48">
+        <v>100</v>
+      </c>
+      <c r="H48" t="s">
+        <v>12</v>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
+      <c r="D49" t="s">
+        <v>83</v>
+      </c>
+      <c r="E49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49">
+        <v>20</v>
+      </c>
+      <c r="G49">
+        <v>20</v>
+      </c>
+      <c r="H49" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>84</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <v>3</v>
+      </c>
+      <c r="D50" t="s">
+        <v>85</v>
+      </c>
+      <c r="E50" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50">
+        <v>100</v>
+      </c>
+      <c r="G50">
+        <v>100</v>
+      </c>
+      <c r="H50" t="s">
+        <v>12</v>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>84</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51">
+        <v>3</v>
+      </c>
+      <c r="D51" t="s">
+        <v>86</v>
+      </c>
+      <c r="E51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F51">
+        <v>20</v>
+      </c>
+      <c r="G51">
+        <v>20</v>
+      </c>
+      <c r="H51" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>87</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52" t="s">
+        <v>88</v>
+      </c>
+      <c r="E52" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52">
+        <v>100</v>
+      </c>
+      <c r="G52">
+        <v>100</v>
+      </c>
+      <c r="H52" t="s">
+        <v>12</v>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>87</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
+      </c>
+      <c r="D53" t="s">
+        <v>89</v>
+      </c>
+      <c r="E53" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53">
+        <v>20</v>
+      </c>
+      <c r="G53">
+        <v>20</v>
+      </c>
+      <c r="H53" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>90</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="D54" t="s">
+        <v>91</v>
+      </c>
+      <c r="E54" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54">
+        <v>100</v>
+      </c>
+      <c r="G54">
+        <v>100</v>
+      </c>
+      <c r="H54" t="s">
+        <v>12</v>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>90</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55" t="s">
+        <v>92</v>
+      </c>
+      <c r="E55" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55">
+        <v>20</v>
+      </c>
+      <c r="G55">
+        <v>20</v>
+      </c>
+      <c r="H55" t="s">
+        <v>14</v>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>93</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56">
+        <v>3</v>
+      </c>
+      <c r="D56" t="s">
+        <v>94</v>
+      </c>
+      <c r="E56" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56">
+        <v>100</v>
+      </c>
+      <c r="G56">
+        <v>100</v>
+      </c>
+      <c r="H56" t="s">
+        <v>12</v>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>93</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57" t="s">
+        <v>95</v>
+      </c>
+      <c r="E57" t="s">
+        <v>14</v>
+      </c>
+      <c r="F57">
+        <v>20</v>
+      </c>
+      <c r="G57">
+        <v>20</v>
+      </c>
+      <c r="H57" t="s">
+        <v>14</v>
+      </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>96</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58">
+        <v>3</v>
+      </c>
+      <c r="D58" t="s">
+        <v>97</v>
+      </c>
+      <c r="E58" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58">
+        <v>100</v>
+      </c>
+      <c r="G58">
+        <v>100</v>
+      </c>
+      <c r="H58" t="s">
+        <v>12</v>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>96</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59">
+        <v>3</v>
+      </c>
+      <c r="D59" t="s">
+        <v>98</v>
+      </c>
+      <c r="E59" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59">
+        <v>20</v>
+      </c>
+      <c r="G59">
+        <v>20</v>
+      </c>
+      <c r="H59" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>99</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60">
+        <v>3</v>
+      </c>
+      <c r="D60" t="s">
+        <v>100</v>
+      </c>
+      <c r="E60" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60">
+        <v>100</v>
+      </c>
+      <c r="G60">
+        <v>100</v>
+      </c>
+      <c r="H60" t="s">
+        <v>12</v>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>99</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61">
+        <v>3</v>
+      </c>
+      <c r="D61" t="s">
+        <v>101</v>
+      </c>
+      <c r="E61" t="s">
+        <v>14</v>
+      </c>
+      <c r="F61">
+        <v>20</v>
+      </c>
+      <c r="G61">
+        <v>20</v>
+      </c>
+      <c r="H61" t="s">
+        <v>14</v>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>102</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62">
+        <v>3</v>
+      </c>
+      <c r="D62" t="s">
+        <v>103</v>
+      </c>
+      <c r="E62" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62">
+        <v>100</v>
+      </c>
+      <c r="G62">
+        <v>100</v>
+      </c>
+      <c r="H62" t="s">
+        <v>12</v>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>102</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63">
+        <v>3</v>
+      </c>
+      <c r="D63" t="s">
+        <v>104</v>
+      </c>
+      <c r="E63" t="s">
+        <v>14</v>
+      </c>
+      <c r="F63">
+        <v>20</v>
+      </c>
+      <c r="G63">
+        <v>20</v>
+      </c>
+      <c r="H63" t="s">
+        <v>14</v>
+      </c>
+      <c r="I63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>105</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64" t="s">
+        <v>106</v>
+      </c>
+      <c r="E64" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64">
+        <v>100</v>
+      </c>
+      <c r="G64">
+        <v>100</v>
+      </c>
+      <c r="H64" t="s">
+        <v>12</v>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>105</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65">
+        <v>3</v>
+      </c>
+      <c r="D65" t="s">
+        <v>107</v>
+      </c>
+      <c r="E65" t="s">
+        <v>14</v>
+      </c>
+      <c r="F65">
+        <v>20</v>
+      </c>
+      <c r="G65">
+        <v>20</v>
+      </c>
+      <c r="H65" t="s">
+        <v>14</v>
+      </c>
+      <c r="I65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>108</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66">
+        <v>3</v>
+      </c>
+      <c r="D66" t="s">
+        <v>109</v>
+      </c>
+      <c r="E66" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66">
+        <v>100</v>
+      </c>
+      <c r="G66">
+        <v>100</v>
+      </c>
+      <c r="H66" t="s">
+        <v>12</v>
+      </c>
+      <c r="I66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>108</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+      <c r="D67" t="s">
+        <v>110</v>
+      </c>
+      <c r="E67" t="s">
+        <v>14</v>
+      </c>
+      <c r="F67">
+        <v>20</v>
+      </c>
+      <c r="G67">
+        <v>20</v>
+      </c>
+      <c r="H67" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>111</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="D68" t="s">
+        <v>112</v>
+      </c>
+      <c r="E68" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68">
+        <v>100</v>
+      </c>
+      <c r="G68">
+        <v>100</v>
+      </c>
+      <c r="H68" t="s">
+        <v>12</v>
+      </c>
+      <c r="I68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>111</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69">
+        <v>3</v>
+      </c>
+      <c r="D69" t="s">
+        <v>113</v>
+      </c>
+      <c r="E69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69">
+        <v>20</v>
+      </c>
+      <c r="G69">
+        <v>20</v>
+      </c>
+      <c r="H69" t="s">
+        <v>14</v>
+      </c>
+      <c r="I69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>114</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="D70" t="s">
+        <v>115</v>
+      </c>
+      <c r="E70" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70">
+        <v>100</v>
+      </c>
+      <c r="G70">
+        <v>100</v>
+      </c>
+      <c r="H70" t="s">
+        <v>12</v>
+      </c>
+      <c r="I70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>114</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="C71">
+        <v>3</v>
+      </c>
+      <c r="D71" t="s">
+        <v>116</v>
+      </c>
+      <c r="E71" t="s">
+        <v>14</v>
+      </c>
+      <c r="F71">
+        <v>20</v>
+      </c>
+      <c r="G71">
+        <v>20</v>
+      </c>
+      <c r="H71" t="s">
+        <v>14</v>
+      </c>
+      <c r="I71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>117</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="C72">
+        <v>3</v>
+      </c>
+      <c r="D72" t="s">
+        <v>118</v>
+      </c>
+      <c r="E72" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72">
+        <v>100</v>
+      </c>
+      <c r="G72">
+        <v>100</v>
+      </c>
+      <c r="H72" t="s">
+        <v>12</v>
+      </c>
+      <c r="I72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>117</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="C73">
+        <v>3</v>
+      </c>
+      <c r="D73" t="s">
+        <v>119</v>
+      </c>
+      <c r="E73" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73">
+        <v>20</v>
+      </c>
+      <c r="G73">
+        <v>20</v>
+      </c>
+      <c r="H73" t="s">
+        <v>14</v>
+      </c>
+      <c r="I73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>120</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74">
+        <v>3</v>
+      </c>
+      <c r="D74" t="s">
+        <v>121</v>
+      </c>
+      <c r="E74" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74">
+        <v>100</v>
+      </c>
+      <c r="G74">
+        <v>100</v>
+      </c>
+      <c r="H74" t="s">
+        <v>12</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>120</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75">
+        <v>3</v>
+      </c>
+      <c r="D75" t="s">
+        <v>122</v>
+      </c>
+      <c r="E75" t="s">
+        <v>14</v>
+      </c>
+      <c r="F75">
+        <v>20</v>
+      </c>
+      <c r="G75">
+        <v>20</v>
+      </c>
+      <c r="H75" t="s">
+        <v>14</v>
+      </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>123</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76">
+        <v>3</v>
+      </c>
+      <c r="D76" t="s">
+        <v>124</v>
+      </c>
+      <c r="E76" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76">
+        <v>100</v>
+      </c>
+      <c r="G76">
+        <v>100</v>
+      </c>
+      <c r="H76" t="s">
+        <v>12</v>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>123</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77">
+        <v>3</v>
+      </c>
+      <c r="D77" t="s">
+        <v>125</v>
+      </c>
+      <c r="E77" t="s">
+        <v>14</v>
+      </c>
+      <c r="F77">
+        <v>20</v>
+      </c>
+      <c r="G77">
+        <v>20</v>
+      </c>
+      <c r="H77" t="s">
+        <v>14</v>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>126</v>
+      </c>
+      <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="C78">
+        <v>3</v>
+      </c>
+      <c r="D78" t="s">
+        <v>127</v>
+      </c>
+      <c r="E78" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78">
+        <v>100</v>
+      </c>
+      <c r="G78">
+        <v>100</v>
+      </c>
+      <c r="H78" t="s">
+        <v>12</v>
+      </c>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>126</v>
+      </c>
+      <c r="B79">
+        <v>1</v>
+      </c>
+      <c r="C79">
+        <v>3</v>
+      </c>
+      <c r="D79" t="s">
+        <v>128</v>
+      </c>
+      <c r="E79" t="s">
+        <v>14</v>
+      </c>
+      <c r="F79">
+        <v>20</v>
+      </c>
+      <c r="G79">
+        <v>20</v>
+      </c>
+      <c r="H79" t="s">
+        <v>14</v>
+      </c>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>129</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80">
+        <v>3</v>
+      </c>
+      <c r="D80" t="s">
+        <v>130</v>
+      </c>
+      <c r="E80" t="s">
+        <v>11</v>
+      </c>
+      <c r="F80">
+        <v>100</v>
+      </c>
+      <c r="G80">
+        <v>100</v>
+      </c>
+      <c r="H80" t="s">
+        <v>12</v>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>129</v>
+      </c>
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81">
+        <v>3</v>
+      </c>
+      <c r="D81" t="s">
+        <v>131</v>
+      </c>
+      <c r="E81" t="s">
+        <v>14</v>
+      </c>
+      <c r="F81">
+        <v>20</v>
+      </c>
+      <c r="G81">
+        <v>20</v>
+      </c>
+      <c r="H81" t="s">
+        <v>14</v>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>132</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82">
+        <v>3</v>
+      </c>
+      <c r="D82" t="s">
+        <v>133</v>
+      </c>
+      <c r="E82" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82">
+        <v>100</v>
+      </c>
+      <c r="G82">
+        <v>100</v>
+      </c>
+      <c r="H82" t="s">
+        <v>12</v>
+      </c>
+      <c r="I82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>132</v>
+      </c>
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83">
+        <v>3</v>
+      </c>
+      <c r="D83" t="s">
+        <v>134</v>
+      </c>
+      <c r="E83" t="s">
+        <v>14</v>
+      </c>
+      <c r="F83">
+        <v>20</v>
+      </c>
+      <c r="G83">
+        <v>20</v>
+      </c>
+      <c r="H83" t="s">
+        <v>14</v>
+      </c>
+      <c r="I83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>135</v>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84">
+        <v>3</v>
+      </c>
+      <c r="D84" t="s">
+        <v>136</v>
+      </c>
+      <c r="E84" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84">
+        <v>100</v>
+      </c>
+      <c r="G84">
+        <v>100</v>
+      </c>
+      <c r="H84" t="s">
+        <v>12</v>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>135</v>
+      </c>
+      <c r="B85">
+        <v>1</v>
+      </c>
+      <c r="C85">
+        <v>3</v>
+      </c>
+      <c r="D85" t="s">
+        <v>137</v>
+      </c>
+      <c r="E85" t="s">
+        <v>14</v>
+      </c>
+      <c r="F85">
+        <v>20</v>
+      </c>
+      <c r="G85">
+        <v>20</v>
+      </c>
+      <c r="H85" t="s">
+        <v>14</v>
+      </c>
+      <c r="I85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>138</v>
+      </c>
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86">
+        <v>3</v>
+      </c>
+      <c r="D86" t="s">
+        <v>139</v>
+      </c>
+      <c r="E86" t="s">
+        <v>11</v>
+      </c>
+      <c r="F86">
+        <v>100</v>
+      </c>
+      <c r="G86">
+        <v>100</v>
+      </c>
+      <c r="H86" t="s">
+        <v>12</v>
+      </c>
+      <c r="I86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>138</v>
+      </c>
+      <c r="B87">
+        <v>1</v>
+      </c>
+      <c r="C87">
+        <v>3</v>
+      </c>
+      <c r="D87" t="s">
         <v>140</v>
       </c>
-      <c r="E3" t="str">
-        <v>Organic turmeric with warm A2 milk</v>
-      </c>
-      <c r="F3" t="str">
-        <v>100% Organic, Vegan</v>
-      </c>
-      <c r="G3">
+      <c r="E87" t="s">
+        <v>14</v>
+      </c>
+      <c r="F87">
+        <v>20</v>
+      </c>
+      <c r="G87">
+        <v>20</v>
+      </c>
+      <c r="H87" t="s">
+        <v>14</v>
+      </c>
+      <c r="I87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>141</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88">
+        <v>3</v>
+      </c>
+      <c r="D88" t="s">
+        <v>142</v>
+      </c>
+      <c r="E88" t="s">
+        <v>11</v>
+      </c>
+      <c r="F88">
+        <v>100</v>
+      </c>
+      <c r="G88">
+        <v>100</v>
+      </c>
+      <c r="H88" t="s">
+        <v>12</v>
+      </c>
+      <c r="I88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>141</v>
+      </c>
+      <c r="B89">
+        <v>1</v>
+      </c>
+      <c r="C89">
+        <v>3</v>
+      </c>
+      <c r="D89" t="s">
+        <v>143</v>
+      </c>
+      <c r="E89" t="s">
+        <v>14</v>
+      </c>
+      <c r="F89">
+        <v>20</v>
+      </c>
+      <c r="G89">
+        <v>20</v>
+      </c>
+      <c r="H89" t="s">
+        <v>14</v>
+      </c>
+      <c r="I89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>144</v>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+      <c r="C90">
+        <v>3</v>
+      </c>
+      <c r="D90" t="s">
+        <v>145</v>
+      </c>
+      <c r="E90" t="s">
+        <v>11</v>
+      </c>
+      <c r="F90">
+        <v>100</v>
+      </c>
+      <c r="G90">
+        <v>100</v>
+      </c>
+      <c r="H90" t="s">
+        <v>12</v>
+      </c>
+      <c r="I90" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>144</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91">
+        <v>3</v>
+      </c>
+      <c r="D91" t="s">
+        <v>146</v>
+      </c>
+      <c r="E91" t="s">
+        <v>14</v>
+      </c>
+      <c r="F91">
+        <v>20</v>
+      </c>
+      <c r="G91">
+        <v>20</v>
+      </c>
+      <c r="H91" t="s">
+        <v>14</v>
+      </c>
+      <c r="I91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>147</v>
+      </c>
+      <c r="B92">
+        <v>1</v>
+      </c>
+      <c r="C92">
+        <v>3</v>
+      </c>
+      <c r="D92" t="s">
+        <v>148</v>
+      </c>
+      <c r="E92" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92">
+        <v>100</v>
+      </c>
+      <c r="G92">
+        <v>100</v>
+      </c>
+      <c r="H92" t="s">
+        <v>12</v>
+      </c>
+      <c r="I92" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>147</v>
+      </c>
+      <c r="B93">
+        <v>1</v>
+      </c>
+      <c r="C93">
+        <v>3</v>
+      </c>
+      <c r="D93" t="s">
+        <v>149</v>
+      </c>
+      <c r="E93" t="s">
+        <v>14</v>
+      </c>
+      <c r="F93">
+        <v>20</v>
+      </c>
+      <c r="G93">
+        <v>20</v>
+      </c>
+      <c r="H93" t="s">
+        <v>14</v>
+      </c>
+      <c r="I93" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
         <v>150</v>
       </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>18</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
+      <c r="B94">
+        <v>1</v>
+      </c>
+      <c r="C94">
+        <v>3</v>
+      </c>
+      <c r="D94" t="s">
+        <v>151</v>
+      </c>
+      <c r="E94" t="s">
+        <v>11</v>
+      </c>
+      <c r="F94">
+        <v>100</v>
+      </c>
+      <c r="G94">
+        <v>100</v>
+      </c>
+      <c r="H94" t="s">
+        <v>12</v>
+      </c>
+      <c r="I94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>150</v>
+      </c>
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="C95">
+        <v>3</v>
+      </c>
+      <c r="D95" t="s">
+        <v>152</v>
+      </c>
+      <c r="E95" t="s">
+        <v>14</v>
+      </c>
+      <c r="F95">
+        <v>20</v>
+      </c>
+      <c r="G95">
+        <v>20</v>
+      </c>
+      <c r="H95" t="s">
+        <v>14</v>
+      </c>
+      <c r="I95" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>153</v>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96">
+        <v>3</v>
+      </c>
+      <c r="D96" t="s">
+        <v>154</v>
+      </c>
+      <c r="E96" t="s">
+        <v>11</v>
+      </c>
+      <c r="F96">
+        <v>100</v>
+      </c>
+      <c r="G96">
+        <v>100</v>
+      </c>
+      <c r="H96" t="s">
+        <v>12</v>
+      </c>
+      <c r="I96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>153</v>
+      </c>
+      <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="C97">
+        <v>3</v>
+      </c>
+      <c r="D97" t="s">
+        <v>155</v>
+      </c>
+      <c r="E97" t="s">
+        <v>14</v>
+      </c>
+      <c r="F97">
+        <v>20</v>
+      </c>
+      <c r="G97">
+        <v>20</v>
+      </c>
+      <c r="H97" t="s">
+        <v>14</v>
+      </c>
+      <c r="I97" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J3"/>
+    <ignoredError sqref="A1:I1 A3:B97 A2:B2 D2:I2 D3:I97" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>